--- a/04_DESIGN_TABLES/DesignTable_2605.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2605.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -712,12 +712,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Air-Way s173 only (double-pass 31 rows); pass1 stated ROWS=32 but enumerated 31; pass2 31; Series sheet n=30 -&gt; 31 accepted (both passes agree)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on Y@HEX=0.56~0.562; D_1@BORE=0.17~0.172; D1@BORE=0.28~0.281; D3@BORE=0.17~0.172</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -928,12 +933,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Air-Way s173 only (double-pass 31 rows); pass1 stated ROWS=32 but enumerated 31; pass2 31; Series sheet n=30 -&gt; 31 accepted (both passes agree)</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on Y@HEX=0.56~0.562; D_1@BORE=0.3~0.297; D1@BORE=0.28~0.281; D3@BORE=0.3~0.297</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1026,13 +1036,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="C10" t="n">
         <v>1.22</v>
       </c>
       <c r="D10" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="E10" t="n">
         <v>0.75</v>
@@ -1077,7 +1087,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Air-Way s173 only (double-pass 31 rows); pass1 stated ROWS=32 but enumerated 31; pass2 31; Series sheet n=30 -&gt; 31 accepted (both passes agree)</t>
+          <t>Air-Way s173 only (double-pass 31 rows); pass1 stated ROWS=32 but enumerated 31; pass2 31; Series sheet n=30 -&gt; 31 accepted (both passes agree); M1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N837 = 1.140 (table had 1.06) [user 2026-10-18 A19]; M3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P837 = 1.140 (table had 1.06) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): M1@DRIVE 1.06 -&gt; OMi 1.140 (Items!N837, M186) | A19 (user 2026-10-18, group 3 open): M3@DRIVE 1.06 -&gt; OMi 1.140 (Items!P837, M188)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1576,12 +1591,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Air-Way s173 only (double-pass 31 rows); pass1 stated ROWS=32 but enumerated 31; pass2 31; Series sheet n=30 -&gt; 31 accepted (both passes agree)</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on Y@HEX=0.88~0.875; D_1@BORE=0.39~0.391; D1@BORE=0.53~0.531; D3@BORE=0.39~0.391</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2080,12 +2100,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Air-Way s173 only (double-pass 31 rows); pass1 stated ROWS=32 but enumerated 31; pass2 31; Series sheet n=30 -&gt; 31 accepted (both passes agree)</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on Y@HEX=1.06~1.062; D_1@BORE=0.61~0.609; D1@BORE=0.72~0.719; D3@BORE=0.61~0.609</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2368,12 +2393,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Air-Way s173 only (double-pass 31 rows); pass1 stated ROWS=32 but enumerated 31; pass2 31; Series sheet n=30 -&gt; 31 accepted (both passes agree)</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on Y@HEX=1.31~1.312; D_1@BORE=0.84~0.844; D1@BORE=0.94~0.938; D3@BORE=0.84~0.844</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2512,12 +2542,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Air-Way s173 only (double-pass 31 rows); pass1 stated ROWS=32 but enumerated 31; pass2 31; Series sheet n=30 -&gt; 31 accepted (both passes agree)</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on Y@HEX=1.63~1.625; D_1@BORE=1.08~1.078; D1@BORE=1.25~1.250; D3@BORE=1.08~1.078</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_2605.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2605.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="C10" t="n">
         <v>1.22</v>
       </c>
       <c r="D10" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="E10" t="n">
         <v>0.75</v>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Air-Way s173 only (double-pass 31 rows); pass1 stated ROWS=32 but enumerated 31; pass2 31; Series sheet n=30 -&gt; 31 accepted (both passes agree); M1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N837 = 1.140 (table had 1.06) [user 2026-10-18 A19]; M3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P837 = 1.140 (table had 1.06) [user 2026-10-18 A19]</t>
+          <t>Air-Way s173 only (double-pass 31 rows); pass1 stated ROWS=32 but enumerated 31; pass2 31; Series sheet n=30 -&gt; 31 accepted (both passes agree); M1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N837 = 1.140 (table had 1.06) [user 2026-10-18 A19]; M3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P837 = 1.140 (table had 1.06) [user 2026-10-18 A19]; M1@DRIVE: Air-Way 1.06 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.14) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; M3@DRIVE: Air-Way 1.06 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.14) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): M1@DRIVE 1.06 -&gt; OMi 1.140 (Items!N837, M186) | A19 (user 2026-10-18, group 3 open): M3@DRIVE 1.06 -&gt; OMi 1.140 (Items!P837, M188)</t>
+          <t>A19 (user 2026-10-18, group 3 open): M1@DRIVE 1.06 -&gt; OMi 1.140 (Items!N837, M186) | A19 (user 2026-10-18, group 3 open): M3@DRIVE 1.06 -&gt; OMi 1.140 (Items!P837, M188) | 2026-10-20 Air-Way first: M1@DRIVE OMi/Brennan 1.14 -&gt; Air-Way 1.06 | 2026-10-20 Air-Way first: M3@DRIVE OMi/Brennan 1.14 -&gt; Air-Way 1.06</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
